--- a/data/trans_orig/P13A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según días que sufre dolor de cabeza al mes en 2023</t>
+          <t>Población según cuántos días al mes sufre dolor de cabeza en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58864</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77660</t>
+          <t>77866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106297</t>
+          <t>105597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117655</t>
+          <t>117470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>160914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240315</t>
+          <t>238323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268444</t>
+          <t>267530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154348</t>
+          <t>155675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182200</t>
+          <t>183113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>401367</t>
+          <t>400832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445506</t>
+          <t>446408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37843</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>51838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94394</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139242</t>
+          <t>138784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163381</t>
+          <t>163914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201410</t>
+          <t>202066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270690</t>
+          <t>269347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330206</t>
+          <t>326077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>353384</t>
+          <t>353189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>401169</t>
+          <t>401168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257133</t>
+          <t>255973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>298485</t>
+          <t>296216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>622832</t>
+          <t>621814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>686214</t>
+          <t>686106</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>40215</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60427</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>111238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123291</t>
+          <t>125585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>163896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240261</t>
+          <t>238518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266532</t>
+          <t>266565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197104</t>
+          <t>195222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>228082</t>
+          <t>226825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>443351</t>
+          <t>442267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>486368</t>
+          <t>484293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33013</t>
+          <t>34964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60554</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98996</t>
+          <t>99740</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107759</t>
+          <t>106742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>291391</t>
+          <t>296539</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>180058</t>
+          <t>181389</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>393733</t>
+          <t>381820</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>201767</t>
+          <t>202150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242458</t>
+          <t>241841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161773</t>
+          <t>162655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>321333</t>
+          <t>325299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>359337</t>
+          <t>372791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>554005</t>
+          <t>552182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>56098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>53907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74605</t>
+          <t>73974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>146001</t>
+          <t>146092</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161254</t>
+          <t>161109</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130464</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>148721</t>
+          <t>147872</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282114</t>
+          <t>281926</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>306097</t>
+          <t>306205</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44730</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>49345</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75445</t>
+          <t>75872</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>54308</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>77294</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>110540</t>
+          <t>109740</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>144587</t>
+          <t>144337</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177990</t>
+          <t>177947</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>204910</t>
+          <t>205778</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140361</t>
+          <t>141583</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>165820</t>
+          <t>165741</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>327341</t>
+          <t>326802</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>363302</t>
+          <t>364951</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62957</t>
+          <t>62487</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>31860</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>67285</t>
+          <t>67164</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43230</t>
+          <t>42893</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>55866</t>
+          <t>55561</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>40870</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>87322</t>
+          <t>85935</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>108622</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>161666</t>
+          <t>163334</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>273209</t>
+          <t>272273</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>630607</t>
+          <t>631958</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>387697</t>
+          <t>389173</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>892675</t>
+          <t>937912</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>419374</t>
+          <t>419700</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>474755</t>
+          <t>477217</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>176577</t>
+          <t>171912</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>465781</t>
+          <t>468352</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>497905</t>
+          <t>463644</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>941458</t>
+          <t>938520</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>44344</t>
+          <t>42072</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>45548</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>61407</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>86781</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>70459</t>
+          <t>72039</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>142031</t>
+          <t>145703</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>856107</t>
+          <t>855577</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>907126</t>
+          <t>905435</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>580406</t>
+          <t>583755</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>616844</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1443333</t>
+          <t>1441382</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1541713</t>
+          <t>1542986</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>123979</t>
+          <t>123257</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>183039</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>158378</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>219326</t>
+          <t>223357</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>108457</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>154477</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>216058</t>
+          <t>218063</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>232956</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>313274</t>
+          <t>313323</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>405602</t>
+          <t>420364</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>602100</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>939748</t>
+          <t>943842</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1584187</t>
+          <t>1715778</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1435920</t>
+          <t>1450980</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2281642</t>
+          <t>2217312</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2715355</t>
+          <t>2713849</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2953391</t>
+          <t>2934164</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1779155</t>
+          <t>1681044</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2343231</t>
+          <t>2339168</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4505642</t>
+          <t>4464031</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5221174</t>
+          <t>5191148</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>27307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47610</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45345</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90860</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77866</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105597</t>
+          <t>105144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>136205</t>
+          <t>138825</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117470</t>
+          <t>121753</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160914</t>
+          <t>158715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>255766</t>
+          <t>259547</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238323</t>
+          <t>245709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267530</t>
+          <t>272599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>169664</t>
+          <t>193412</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155675</t>
+          <t>178833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183113</t>
+          <t>207493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>425429</t>
+          <t>452959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>400832</t>
+          <t>432071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446408</t>
+          <t>473041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>57367</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21681</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>56250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>115005</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94133</t>
+          <t>98300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138784</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182620</t>
+          <t>191166</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163914</t>
+          <t>171848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202066</t>
+          <t>212317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,27 +1590,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>297625</t>
+          <t>309916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269347</t>
+          <t>279653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326077</t>
+          <t>339893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>379465</t>
+          <t>385354</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>353189</t>
+          <t>362338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>401168</t>
+          <t>409455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>276378</t>
+          <t>297289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255973</t>
+          <t>276750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>296216</t>
+          <t>317255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>655843</t>
+          <t>682643</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>621814</t>
+          <t>648449</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>686106</t>
+          <t>711911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30352</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47313</t>
+          <t>50004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60088</t>
+          <t>63653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>99044</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>85100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111238</t>
+          <t>114747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>143604</t>
+          <t>149048</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125585</t>
+          <t>131206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163896</t>
+          <t>169843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>253568</t>
+          <t>251178</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238518</t>
+          <t>236385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266565</t>
+          <t>263381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>211684</t>
+          <t>214861</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195222</t>
+          <t>198317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226825</t>
+          <t>229515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>465253</t>
+          <t>466039</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>442267</t>
+          <t>443436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>484293</t>
+          <t>484373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>313906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345443</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>659397</t>
+          <t>666647</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>34123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78570</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60091</t>
+          <t>70523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99740</t>
+          <t>116804</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166919</t>
+          <t>110116</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106742</t>
+          <t>93509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>296539</t>
+          <t>127474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>245489</t>
+          <t>200111</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181389</t>
+          <t>172814</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>381820</t>
+          <t>233632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>223077</t>
+          <t>270066</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202150</t>
+          <t>243839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241841</t>
+          <t>290622</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>268048</t>
+          <t>266688</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162655</t>
+          <t>247479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>325299</t>
+          <t>285522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>491125</t>
+          <t>536754</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372791</t>
+          <t>503977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>552182</t>
+          <t>564004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311873</t>
+          <t>372363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>474609</t>
+          <t>420833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>786482</t>
+          <t>793196</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3011,57 +3011,57 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8727</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>4620</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8386</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>41989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>58998</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53907</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>155068</t>
+          <t>180332</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>146092</t>
+          <t>171484</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161109</t>
+          <t>186569</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>140015</t>
+          <t>154465</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130103</t>
+          <t>144534</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>147872</t>
+          <t>163310</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>295083</t>
+          <t>334796</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>281926</t>
+          <t>320064</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>306205</t>
+          <t>346575</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>34995</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>34367</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>61175</t>
+          <t>62448</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75872</t>
+          <t>76580</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>64892</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>126067</t>
+          <t>128114</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>109740</t>
+          <t>112399</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>144337</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>192676</t>
+          <t>192705</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177947</t>
+          <t>177866</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>205778</t>
+          <t>204284</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>153916</t>
+          <t>158882</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>141583</t>
+          <t>145366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>165741</t>
+          <t>170985</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>346591</t>
+          <t>351587</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>326802</t>
+          <t>333125</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>364951</t>
+          <t>369571</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269295</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>256660</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>533710</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62487</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>67164</t>
+          <t>77644</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26812</t>
+          <t>27866</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42893</t>
+          <t>45431</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>55561</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>64577</t>
+          <t>72688</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>85935</t>
+          <t>93127</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>132269</t>
+          <t>151583</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>108004</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>163334</t>
+          <t>178264</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>417695</t>
+          <t>255892</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>272273</t>
+          <t>230700</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>631958</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>549964</t>
+          <t>407474</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>389173</t>
+          <t>371060</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>937912</t>
+          <t>444016</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>450075</t>
+          <t>521931</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>419700</t>
+          <t>494903</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>477217</t>
+          <t>551442</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>346664</t>
+          <t>412138</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>171912</t>
+          <t>384932</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>468352</t>
+          <t>438926</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>796738</t>
+          <t>934069</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>463644</t>
+          <t>892429</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>938520</t>
+          <t>971918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>710293</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>765351</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1462244</t>
+          <t>1475643</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>42072</t>
+          <t>32346</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>47351</t>
+          <t>35290</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>36939</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>62864</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>73719</t>
+          <t>85162</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>61407</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>86781</t>
+          <t>100578</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>134012</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>72039</t>
+          <t>113280</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>145703</t>
+          <t>154679</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>878620</t>
+          <t>739720</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>855577</t>
+          <t>724507</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>905435</t>
+          <t>752380</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>601309</t>
+          <t>702467</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>583755</t>
+          <t>684599</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>618171</t>
+          <t>718789</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1479929</t>
+          <t>1442187</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1441382</t>
+          <t>1416151</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1542986</t>
+          <t>1464509</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796931</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>712809</t>
+          <t>825079</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1640504</t>
+          <t>1622010</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>123257</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>183039</t>
+          <t>188685</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>161946</t>
+          <t>177943</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>223357</t>
+          <t>233433</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>64389</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>108457</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>188642</t>
+          <t>204432</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>154477</t>
+          <t>182657</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>218063</t>
+          <t>230380</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>273422</t>
+          <t>296299</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>264888</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>313323</t>
+          <t>330452</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>537582</t>
+          <t>586408</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>420364</t>
+          <t>539350</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>603837</t>
+          <t>637824</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1140195</t>
+          <t>948117</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>943842</t>
+          <t>905681</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1715778</t>
+          <t>995157</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1677777</t>
+          <t>1534525</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1450980</t>
+          <t>1464905</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2217312</t>
+          <t>1598495</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2788314</t>
+          <t>2800833</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2713849</t>
+          <t>2744798</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2934164</t>
+          <t>2847721</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2167677</t>
+          <t>2400202</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1681044</t>
+          <t>2350329</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2339168</t>
+          <t>2449004</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4955991</t>
+          <t>5201035</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4464031</t>
+          <t>5132037</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5191148</t>
+          <t>5276229</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
